--- a/artfynd/A 41104-2025 artfynd.xlsx
+++ b/artfynd/A 41104-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>61641956</v>
       </c>
       <c r="B2" t="n">
-        <v>56286</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,7 +695,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458991.3708879511</v>
+        <v>458991</v>
       </c>
       <c r="R2" t="n">
-        <v>6401476.787649103</v>
+        <v>6401477</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -798,32 +793,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>61641952</v>
+        <v>61641948</v>
       </c>
       <c r="B3" t="n">
-        <v>56311</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100067</v>
+        <v>100065</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -833,18 +823,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>6150</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -853,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458991.3708879511</v>
+        <v>458991</v>
       </c>
       <c r="R3" t="n">
-        <v>6401476.787649103</v>
+        <v>6401477</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -922,6 +908,128 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>61641952</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sörskogen, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>458991</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6401477</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hakarp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2016-10-03</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2016-10-03</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41104-2025 artfynd.xlsx
+++ b/artfynd/A 41104-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61641956</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61641948</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1030,8 +1045,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61641952</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>